--- a/efficacity_data_v1.xlsx
+++ b/efficacity_data_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siapartners1-my.sharepoint.com/personal/mathian_akanati_sia-partners_com/Documents/Documents/Lab RO/Efficacity/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youss\Desktop\Projet ST7\sia_efficacity_projet_st7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{96212DCE-59AB-42DC-B396-7FE63F953CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{768B0E00-652E-4D38-91CA-20D5114AD6D2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919D614C-003A-4B7A-AAA9-AD91D28A4D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12154" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12154" uniqueCount="1019">
   <si>
     <t>id_simulation</t>
   </si>
@@ -3091,9 +3091,6 @@
   </si>
   <si>
     <t>Booléen qui précise si plusieurs actions ont été modélisées dans la simulation. "True" = au moins 2 actions, "False" = au plus 1 action.</t>
-  </si>
-  <si>
-    <t>rzea</t>
   </si>
   <si>
     <t>building_type</t>
@@ -3669,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -10722,7 +10719,7 @@
         <v>843</v>
       </c>
       <c r="B73" t="s">
-        <v>1018</v>
+        <v>837</v>
       </c>
       <c r="C73" t="s">
         <v>232</v>
@@ -88459,17 +88456,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="df7fba94-3066-4f9e-b6b3-2937642b633c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3db8c227-7cc4-411e-bd2d-91868851af27">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100379511CCFB86484CA8BB4D9F99A360CA" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="ed178687dc9713501e7afa22b47b93f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3db8c227-7cc4-411e-bd2d-91868851af27" xmlns:ns3="df7fba94-3066-4f9e-b6b3-2937642b633c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d36b47eafa71096f7cae34510f412ee3" ns2:_="" ns3:_="">
     <xsd:import namespace="3db8c227-7cc4-411e-bd2d-91868851af27"/>
@@ -88698,6 +88684,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="df7fba94-3066-4f9e-b6b3-2937642b633c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3db8c227-7cc4-411e-bd2d-91868851af27">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -88708,17 +88705,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A08660D-1512-449F-9AA7-33C5D198C055}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="df7fba94-3066-4f9e-b6b3-2937642b633c"/>
-    <ds:schemaRef ds:uri="3db8c227-7cc4-411e-bd2d-91868851af27"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D4FF77D-62D3-4E5B-9FC2-4E2BC3DF1FE1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -88737,6 +88723,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A08660D-1512-449F-9AA7-33C5D198C055}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="df7fba94-3066-4f9e-b6b3-2937642b633c"/>
+    <ds:schemaRef ds:uri="3db8c227-7cc4-411e-bd2d-91868851af27"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D300C3D-25B2-4746-A892-8D65969DF71B}">
   <ds:schemaRefs>
